--- a/Results_2024Pricing/Market Price Model/August/Market_August_2024.xlsx
+++ b/Results_2024Pricing/Market Price Model/August/Market_August_2024.xlsx
@@ -5,11 +5,11 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Months of 2018\August 2018\Market-Contract Price Model\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\OneDrive - Washington State University (email.wsu.edu)\Documents\GitHub\BugFlowExperiment_Analysis2026\Results_2024Pricing\Market Price Model\August\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="21570" windowHeight="8925"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="21570" windowHeight="8925" firstSheet="29" activeTab="40"/>
   </bookViews>
   <sheets>
     <sheet name="Table of Contents" sheetId="46" r:id="rId1"/>
@@ -1124,6 +1124,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E83"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="34.28515625" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
